--- a/dataset/construct/dataset_splits/data_size/20_percent/tum/fold5.xlsx
+++ b/dataset/construct/dataset_splits/data_size/20_percent/tum/fold5.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN11"/>
+  <dimension ref="A1:AK11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,185 +446,170 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>BMI</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>BMI</t>
+          <t>AFPRE</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>CABGPRE</t>
+          <t>LVEFPRE</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>AFPRE</t>
+          <t>PREDILATION</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>LVEFPRE</t>
+          <t>CT_ValScNCC</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>NTPROBNPPRE</t>
+          <t>CT_ValScRCC</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>PREDILATION</t>
+          <t>CT_ValScLCC</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScNCC</t>
+          <t>CT_ValvScTot</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScRCC</t>
+          <t>CT_AnnScNCC</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScLCC</t>
+          <t>CT_AnnScRCC</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValvScTot</t>
+          <t>CT_AnnScLCC</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScNCC</t>
+          <t>CT_AnnScTot</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScRCC</t>
+          <t>CT_LVOTScNCC</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScLCC</t>
+          <t>CT_LVOTScRCC</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScTot</t>
+          <t>CT_LVOTScLCC</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScNCC</t>
+          <t>CT_LVOTScTot</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScRCC</t>
+          <t>SEX</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScLCC</t>
+          <t>CT_AnnMean</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScTot</t>
+          <t>ECC_INDEX</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>SEX</t>
+          <t>CT_Peri_Deri</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnMean</t>
+          <t>CT_Area_Deri</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>ECC_INDEX</t>
+          <t>nyha2</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>CT_Peri_Deri</t>
+          <t>nyha3</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>CT_Area_Deri</t>
+          <t>nyha4</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>nyha2</t>
+          <t>model1</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>nyha3</t>
+          <t>model2</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>nyha4</t>
+          <t>model3</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>model1</t>
+          <t>model4</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>model2</t>
+          <t>model7</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>model3</t>
+          <t>model8</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>model4</t>
+          <t>brand2</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>model7</t>
+          <t>brand8</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>model8</t>
+          <t>QRSADM</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>brand2</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>brand8</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>QRSADM</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>PQADM</t>
         </is>
@@ -632,7 +617,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1492</v>
+        <v>2308</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -640,85 +625,85 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>80.88521056734351</v>
+        <v>76.85541314928891</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>28.2828282828282</v>
       </c>
       <c r="E2" t="n">
-        <v>27.6816608996539</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>60</v>
+        <v>387.4</v>
       </c>
       <c r="I2" t="n">
-        <v>900</v>
+        <v>356.4</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>395.4</v>
       </c>
       <c r="K2" t="n">
-        <v>804.3</v>
+        <v>1139.2</v>
       </c>
       <c r="L2" t="n">
-        <v>478.3</v>
+        <v>119.7</v>
       </c>
       <c r="M2" t="n">
-        <v>399.3</v>
+        <v>53.2</v>
       </c>
       <c r="N2" t="n">
-        <v>1681.9</v>
+        <v>175.5</v>
       </c>
       <c r="O2" t="n">
-        <v>34.8</v>
+        <v>348.4</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>14.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>42.4</v>
+        <v>127.4</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>142.3</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>23.05</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>22.8545963840081</v>
       </c>
       <c r="X2" t="n">
-        <v>25.45</v>
+        <v>22.1741916431478</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.188612099644128</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="n">
-        <v>25.6238859180036</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>25.3430608104398</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
@@ -730,7 +715,7 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
         <v>0</v>
@@ -739,22 +724,15 @@
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="AK2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>86</v>
-      </c>
-      <c r="AN2" t="inlineStr"/>
+        <v>256</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>320</v>
+        <v>520</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -762,83 +740,85 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>80.3924023373134</v>
+        <v>91.96256179177119</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>24.4646016033723</v>
       </c>
       <c r="E3" t="n">
-        <v>22.189349112426</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>50</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
+        <v>503</v>
+      </c>
+      <c r="I3" t="n">
+        <v>648</v>
+      </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>259</v>
       </c>
       <c r="K3" t="n">
-        <v>160</v>
+        <v>1410</v>
       </c>
       <c r="L3" t="n">
-        <v>145</v>
+        <v>20</v>
       </c>
       <c r="M3" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="N3" t="n">
-        <v>322</v>
+        <v>163</v>
       </c>
       <c r="O3" t="n">
-        <v>15</v>
+        <v>190</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>20</v>
+        <v>152</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>23.95</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>23.8731856378915</v>
       </c>
       <c r="X3" t="n">
-        <v>20.75</v>
+        <v>22.9831467948561</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.248945147679325</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>21.3267125031831</v>
+        <v>1</v>
       </c>
       <c r="AA3" t="n">
-        <v>20.6802165106906</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
@@ -847,36 +827,25 @@
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>96</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>156</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="AK3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>598</v>
+        <v>1672</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -884,85 +853,85 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>80.29658529165719</v>
+        <v>85.7315332281289</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>26.0789715335169</v>
       </c>
       <c r="E4" t="n">
-        <v>17.0068027210884</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>60</v>
+        <v>122</v>
       </c>
       <c r="I4" t="n">
-        <v>1630</v>
+        <v>52</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="K4" t="n">
-        <v>32</v>
+        <v>238</v>
       </c>
       <c r="L4" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>238</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>69</v>
+        <v>24.2</v>
       </c>
       <c r="V4" t="n">
-        <v>74</v>
+        <v>0.27</v>
       </c>
       <c r="W4" t="n">
-        <v>2</v>
+        <v>23.8731856378915</v>
       </c>
       <c r="X4" t="n">
-        <v>19.8</v>
+        <v>23.3675988578761</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.285714285714286</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>19.7351667939903</v>
+        <v>1</v>
       </c>
       <c r="AA4" t="n">
-        <v>19.1461601132455</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
@@ -971,10 +940,10 @@
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH4" t="n">
         <v>0</v>
@@ -983,24 +952,15 @@
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AK4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>98</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>180</v>
+        <v>272</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>610</v>
+        <v>361</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1008,79 +968,79 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>80.4444026161685</v>
+        <v>78.027219623799</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>26.6097125450789</v>
       </c>
       <c r="E5" t="n">
-        <v>38.7396694214876</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>45</v>
+        <v>276</v>
       </c>
       <c r="I5" t="n">
-        <v>3400</v>
+        <v>295</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>161</v>
       </c>
       <c r="K5" t="n">
-        <v>966</v>
+        <v>732</v>
       </c>
       <c r="L5" t="n">
-        <v>1037</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>221</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2224</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>24.05</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>24.5098039215686</v>
       </c>
       <c r="X5" t="n">
-        <v>29.95</v>
+        <v>23.7993692983298</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.263768115942029</v>
+        <v>1</v>
       </c>
       <c r="Z5" t="n">
-        <v>31.5126050420168</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>30.3986119121575</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -1107,22 +1067,15 @@
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="AK5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN5" t="inlineStr"/>
+        <v>156</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1736</v>
+        <v>2169</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1130,91 +1083,91 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>86.46788494689081</v>
+        <v>79.1083821646767</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>23.1836734693877</v>
       </c>
       <c r="E6" t="n">
-        <v>24.8579545454545</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>60</v>
+        <v>696.4</v>
       </c>
       <c r="I6" t="n">
-        <v>4130</v>
+        <v>556.8</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>561.3</v>
       </c>
       <c r="K6" t="n">
-        <v>187.8</v>
+        <v>1814.5</v>
       </c>
       <c r="L6" t="n">
-        <v>186.2</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>239</v>
+        <v>44.3</v>
       </c>
       <c r="N6" t="n">
-        <v>613</v>
+        <v>52.8</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>13.8</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>25.25</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>25.6557168321874</v>
       </c>
       <c r="X6" t="n">
-        <v>27.2</v>
+        <v>24.2129335077053</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.192691029900332</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>27.3745861981156</v>
+        <v>1</v>
       </c>
       <c r="AA6" t="n">
-        <v>26.9117274486368</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -1229,22 +1182,13 @@
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN6" t="inlineStr"/>
+        <v>96</v>
+      </c>
+      <c r="AK6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1419</v>
+        <v>796</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1252,41 +1196,43 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>77.95573351585671</v>
+        <v>77.90669860825921</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>28.125</v>
       </c>
       <c r="E7" t="n">
-        <v>33.0578512396694</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>60</v>
-      </c>
-      <c r="I7" t="inlineStr"/>
+        <v>58.9</v>
+      </c>
+      <c r="I7" t="n">
+        <v>34.8</v>
+      </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>31.7</v>
+        <v>159.1</v>
       </c>
       <c r="L7" t="n">
-        <v>38.6</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>12.2</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>82.5</v>
+        <v>16.8</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>16.8</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1301,28 +1247,28 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>22.15</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="W7" t="n">
-        <v>2</v>
+        <v>21.9314998726763</v>
       </c>
       <c r="X7" t="n">
-        <v>20.35</v>
+        <v>21.5128218033123</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.222707423580786</v>
+        <v>1</v>
       </c>
       <c r="Z7" t="n">
-        <v>20.6582633053221</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>20.3326250911699</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
@@ -1337,7 +1283,7 @@
         <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -1349,24 +1295,15 @@
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>180</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1331</v>
+        <v>2123</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1374,91 +1311,91 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>77.67647340101909</v>
+        <v>77.31505558090601</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>22.8930740819877</v>
       </c>
       <c r="E8" t="n">
-        <v>20.7612456747404</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>60</v>
+        <v>590.9</v>
       </c>
       <c r="I8" t="n">
-        <v>1030</v>
+        <v>480</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>205.4</v>
       </c>
       <c r="K8" t="n">
-        <v>296</v>
+        <v>1276.3</v>
       </c>
       <c r="L8" t="n">
-        <v>221</v>
+        <v>13.8</v>
       </c>
       <c r="M8" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="N8" t="n">
-        <v>555</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>8</v>
+        <v>88.8</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="R8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>29.3</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="W8" t="n">
-        <v>2</v>
+        <v>30.143875732111</v>
       </c>
       <c r="X8" t="n">
-        <v>21.85</v>
+        <v>28.9751548801889</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.244979919678715</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>21.9633307868602</v>
+        <v>1</v>
       </c>
       <c r="AA8" t="n">
-        <v>21.4654366757236</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -1467,30 +1404,21 @@
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>92</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>180</v>
+        <v>176</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2642</v>
+        <v>611</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1498,79 +1426,79 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>78.0542406266636</v>
+        <v>86.12057761046469</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>25.390625</v>
       </c>
       <c r="E9" t="n">
-        <v>26.5021162137573</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>59</v>
+        <v>431</v>
       </c>
       <c r="I9" t="n">
-        <v>1460</v>
+        <v>64</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>153</v>
       </c>
       <c r="K9" t="n">
-        <v>323</v>
+        <v>648</v>
       </c>
       <c r="L9" t="n">
-        <v>476</v>
+        <v>50</v>
       </c>
       <c r="M9" t="n">
-        <v>477</v>
+        <v>33</v>
       </c>
       <c r="N9" t="n">
-        <v>1276</v>
+        <v>64</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="P9" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Q9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>22.9</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="W9" t="n">
-        <v>2</v>
+        <v>23.6822001527884</v>
       </c>
       <c r="X9" t="n">
-        <v>24.15</v>
+        <v>22.5639660829322</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.256317689530686</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>24.3188184364655</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>23.866127828619</v>
+        <v>1</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
@@ -1588,33 +1516,22 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>128</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>191</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="AK9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1345</v>
+        <v>598</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1622,79 +1539,79 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>77.4494138971278</v>
+        <v>80.29658529165719</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>17.0068027210884</v>
       </c>
       <c r="E10" t="n">
-        <v>24.3374797187669</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I10" t="n">
-        <v>5850</v>
+        <v>129</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>77</v>
       </c>
       <c r="K10" t="n">
-        <v>40.4</v>
+        <v>238</v>
       </c>
       <c r="L10" t="n">
-        <v>36.5</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>7.6</v>
+        <v>43</v>
       </c>
       <c r="N10" t="n">
-        <v>84.5</v>
+        <v>46</v>
       </c>
       <c r="O10" t="n">
-        <v>4.7</v>
+        <v>89</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.1</v>
+        <v>5</v>
       </c>
       <c r="R10" t="n">
-        <v>5.8</v>
+        <v>69</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>19.8</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>19.7351667939903</v>
       </c>
       <c r="X10" t="n">
-        <v>23.7</v>
+        <v>19.1461601132455</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.211320754716981</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>23.8413547237077</v>
+        <v>1</v>
       </c>
       <c r="AA10" t="n">
-        <v>23.506086798771</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -1721,22 +1638,15 @@
         <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>164</v>
-      </c>
-      <c r="AN10" t="inlineStr"/>
+        <v>180</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>552</v>
+        <v>566</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1744,40 +1654,40 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>84.7838999163434</v>
+        <v>84.7733230663929</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>20.829995193078</v>
       </c>
       <c r="E11" t="n">
-        <v>21.4532871972318</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>60</v>
+        <v>193</v>
       </c>
       <c r="I11" t="n">
-        <v>365</v>
+        <v>75</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>15.8</v>
       </c>
       <c r="K11" t="n">
-        <v>158</v>
+        <v>283.8</v>
       </c>
       <c r="L11" t="n">
-        <v>138</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>383</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1795,28 +1705,28 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U11" t="n">
-        <v>8</v>
+        <v>22.7</v>
       </c>
       <c r="V11" t="n">
-        <v>8</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="n">
-        <v>2</v>
+        <v>22.7909345556404</v>
       </c>
       <c r="X11" t="n">
-        <v>20.65</v>
+        <v>22.4508627838174</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="Z11" t="n">
-        <v>20.3717850776674</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>20.307569474639</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
@@ -1831,32 +1741,21 @@
         <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>86</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>162</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="AK11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
